--- a/data/Lead_information_Formulario_Ecuador_Main.xlsx
+++ b/data/Lead_information_Formulario_Ecuador_Main.xlsx
@@ -481,38 +481,38 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.ec/vans/n400-pasajeros</t>
+          <t>https://www.chevrolet.com.ec/ofertas-autos-suvs-camionetas</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/ecuador/gm_forms/movs-quote-visid?model=n400</t>
+          <t>https://secure-developments.com/commonwealth/ecuador/gm_forms/oportunidades</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Ignacio Valentina</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bravo Gonzalez</t>
+          <t>Morales Perez</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2059185401</t>
+          <t>1325600367</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0952978213</t>
+          <t>0939155859</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ignaciovalentinabravogonzalez_ec80@mrm.com</t>
+          <t>andreamoralesperez_ec23@mrm.com</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -523,38 +523,38 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.ec/flotas-pesados-camiones</t>
+          <t>https://www.chevrolet.com.ec/socios-de-negocio/proveedores</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/ecuador/gm_forms/flotas-pesados?model=flotas%20pesados</t>
+          <t>https://secure-developments.com/commonwealth/ecuador/gm_forms/socios-negocios-proveedores</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Carlos</t>
+          <t>Catalina Fernanda</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Guerrero</t>
+          <t>Cruz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0668822323</t>
+          <t>0762335586</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0998412286</t>
+          <t>0932123906</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>carlosguerrero.ec60@mrm.com</t>
+          <t>catalinafernandacruz.ec34@mrm.com</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -565,38 +565,38 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.chevrolet.com.ec/evento-exhibicion-captiva-ev</t>
+          <t>https://www.chevrolet.com.ec/mantenimiento/prepagado</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://secure-developments.com/commonwealth/ecuador/gm_forms/exhibicion-captiva-ev?model=captiva%20ev</t>
+          <t>https://secure-developments.com/commonwealth/ecuador/gm_forms/mantenimiento-prepaga?model=posventa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Martín Isabella</t>
+          <t>Gabriela Lucía</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Herrera</t>
+          <t>Muñoz</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0744195538</t>
+          <t>2221324086</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0900237217</t>
+          <t>0907456878</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>martinisabellaherrera_ec31@mrm.com</t>
+          <t>gabrielaluciamunoz.ec49@mrm.com</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -618,27 +618,27 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cristian</t>
+          <t>Eduardo Juan</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Reyes</t>
+          <t>García Aguilar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0401750922</t>
+          <t>1433405162</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0998314346</t>
+          <t>0985728211</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>cristianreyes.ec43@mrm.com</t>
+          <t>eduardojuangarciaaguilar.ec45@mrm.com</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
